--- a/Jaipur-February-2026.xlsx
+++ b/Jaipur-February-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="38">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Jaipur</t>
   </si>
   <si>
@@ -112,13 +115,13 @@
     <t>MH02FG4104</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>ETIOS</t>
   </si>
   <si>
-    <t>Dzire</t>
+    <t>DZIRE</t>
   </si>
   <si>
     <t>16/08/2018</t>
@@ -486,10 +489,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:AA7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -568,28 +571,31 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>264</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2026</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H2">
         <v>139690</v>
@@ -649,27 +655,27 @@
         <v>66.91</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>265</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2026</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H3">
         <v>122311</v>
@@ -729,39 +735,39 @@
         <v>60.36</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>266</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2026</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="2">
-        <v>45997</v>
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>36</v>
       </c>
       <c r="H4">
-        <v>23809</v>
+        <v>139690</v>
       </c>
       <c r="I4">
-        <v>28402</v>
+        <v>143486</v>
       </c>
       <c r="J4">
-        <v>4593</v>
+        <v>3796</v>
       </c>
       <c r="K4">
-        <v>4597</v>
+        <v>3886</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -770,13 +776,13 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>4597</v>
+        <v>3886</v>
       </c>
       <c r="O4">
-        <v>-4</v>
+        <v>-90</v>
       </c>
       <c r="P4">
-        <v>111610</v>
+        <v>137405</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -785,108 +791,268 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>111610</v>
+        <v>137405</v>
       </c>
       <c r="T4">
-        <v>26588</v>
+        <v>20672</v>
       </c>
       <c r="U4">
         <v>0</v>
       </c>
       <c r="V4">
-        <v>20145</v>
+        <v>24801</v>
       </c>
       <c r="W4">
-        <v>18470</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>65203</v>
+        <v>45473</v>
       </c>
       <c r="Y4">
-        <v>46407</v>
+        <v>91932</v>
       </c>
       <c r="Z4">
-        <v>41.58</v>
+        <v>66.91</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>267</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2026</v>
       </c>
       <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5">
+        <v>122311</v>
+      </c>
+      <c r="I5">
+        <v>125353</v>
+      </c>
+      <c r="J5">
+        <v>3042</v>
+      </c>
+      <c r="K5">
+        <v>3028</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>3028</v>
+      </c>
+      <c r="O5">
+        <v>14</v>
+      </c>
+      <c r="P5">
+        <v>83770</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>83770</v>
+      </c>
+      <c r="T5">
+        <v>18088</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>15120</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>33208</v>
+      </c>
+      <c r="Y5">
+        <v>50562</v>
+      </c>
+      <c r="Z5">
+        <v>60.36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27">
+      <c r="A6">
+        <v>268</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6">
+        <v>2026</v>
+      </c>
+      <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="2">
+        <v>45997</v>
+      </c>
+      <c r="H6">
+        <v>23809</v>
+      </c>
+      <c r="I6">
+        <v>28402</v>
+      </c>
+      <c r="J6">
+        <v>4593</v>
+      </c>
+      <c r="K6">
+        <v>4597</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>4597</v>
+      </c>
+      <c r="O6">
+        <v>-4</v>
+      </c>
+      <c r="P6">
+        <v>111610</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>111610</v>
+      </c>
+      <c r="T6">
+        <v>26588</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>20145</v>
+      </c>
+      <c r="W6">
+        <v>18470</v>
+      </c>
+      <c r="X6">
+        <v>65203</v>
+      </c>
+      <c r="Y6">
+        <v>46407</v>
+      </c>
+      <c r="Z6">
+        <v>41.58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
+      <c r="A7">
+        <v>269</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7">
+        <v>2026</v>
+      </c>
+      <c r="E7" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="2">
+      <c r="F7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="2">
         <v>44471</v>
       </c>
-      <c r="H5">
+      <c r="H7">
         <v>73824</v>
       </c>
-      <c r="I5">
+      <c r="I7">
         <v>75708</v>
       </c>
-      <c r="J5">
+      <c r="J7">
         <v>1884</v>
       </c>
-      <c r="K5">
+      <c r="K7">
         <v>1770</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
         <v>1770</v>
       </c>
-      <c r="O5">
+      <c r="O7">
         <v>114</v>
       </c>
-      <c r="P5">
+      <c r="P7">
         <v>56945</v>
       </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>56945</v>
       </c>
-      <c r="T5">
+      <c r="T7">
         <v>10766</v>
       </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
         <v>10278</v>
       </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
         <v>21044</v>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <v>35901</v>
       </c>
-      <c r="Z5">
-        <v>63.05</v>
+      <c r="Z7">
+        <v>63.04</v>
       </c>
     </row>
   </sheetData>
